--- a/docs/zelo-ebit-preliminar.xlsx
+++ b/docs/zelo-ebit-preliminar.xlsx
@@ -9,8 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="Premissas" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="EBIT" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Por atendimento" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="DRE 3 anos" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sensibilidade" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Por atendimento" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="129">
   <si>
     <t xml:space="preserve">Zelo — Premissas (todas são hipóteses a validar)</t>
   </si>
@@ -30,13 +31,13 @@
     <t xml:space="preserve">Edite as células em azul. Amarelo = premissas que mais mexem no resultado.</t>
   </si>
   <si>
-    <t xml:space="preserve">PREÇOS (o que a família / empresa paga)</t>
+    <t xml:space="preserve">PREÇOS (o que a família paga)</t>
   </si>
   <si>
     <t xml:space="preserve">Acompanhante (bloco de até 4h)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sugestão do grupo; entrevista: ~R$300 pelo DIA inteiro</t>
+    <t xml:space="preserve">Sugestão do grupo; entrevista: ~R$ 300 pelo DIA inteiro</t>
   </si>
   <si>
     <t xml:space="preserve">Transporte ida e volta (até 15 km)</t>
@@ -60,10 +61,19 @@
     <t xml:space="preserve">Zelo+ (mensal por família)</t>
   </si>
   <si>
-    <t xml:space="preserve">Zelo Empresas (mensal por família inscrita)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empresa paga; família tem Zelo+</t>
+    <t xml:space="preserve">ZELO EMPRESAS (o que a empresa paga)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mensalidade por funcionário (todos os funcionários)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo de benefício: a empresa paga por funcionário, use ou não. Inclui Zelo+ para quem tem pais idosos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funcionários por empresa cliente (média)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empresas médias e grandes de SP</t>
   </si>
   <si>
     <t xml:space="preserve">MIX DOS ATENDIMENTOS</t>
@@ -84,7 +94,7 @@
     <t xml:space="preserve">Repasse ao acompanhante (% do preço)</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimativa; Zelo fica com 25%</t>
+    <t xml:space="preserve">Zelo fica com 25%</t>
   </si>
   <si>
     <t xml:space="preserve">Custo do carro ida e volta (99/Uber/táxi)</t>
@@ -99,7 +109,7 @@
     <t xml:space="preserve">Taxa de pagamento (% do valor cobrado)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cartão/Pix intermediado; estimativa</t>
+    <t xml:space="preserve">Cartão/Pix intermediado; não incide no boleto B2B</t>
   </si>
   <si>
     <t xml:space="preserve">Seguro de acidentes pessoais por atendimento</t>
@@ -108,67 +118,94 @@
     <t xml:space="preserve">IA + WhatsApp por atendimento</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimativa (conversa de agendamento + avisos do dia)</t>
+    <t xml:space="preserve">Conversa de agendamento + avisos do dia</t>
   </si>
   <si>
     <t xml:space="preserve">IA + WhatsApp por família ativa no mês</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimativa (lembretes, perguntas)</t>
+    <t xml:space="preserve">Lembretes, perguntas</t>
   </si>
   <si>
     <t xml:space="preserve">Impostos sobre a receita própria do Zelo</t>
   </si>
   <si>
-    <t xml:space="preserve">Simples Nacional, faixa inicial; estimativa. Base = entradas − repasses − carros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zelo — Entradas, saídas e EBIT preliminar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R$ por mês · cenários hipotéticos · modelo: acompanhante Zelo + carro sob demanda</t>
+    <t xml:space="preserve">Simples Nacional, estimativa. Base = entradas − repasses − carros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zelo — DRE preliminar de 3 anos (R$ por ano)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cenário-base · modelo: acompanhante Zelo + carro sob demanda · B2B cobrado por funcionário</t>
   </si>
   <si>
     <t xml:space="preserve">Linha</t>
   </si>
   <si>
-    <t xml:space="preserve">Piloto (mês 6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fim do ano 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ano 3 (escala SP)</t>
+    <t xml:space="preserve">Ano 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ano 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ano 3</t>
   </si>
   <si>
     <t xml:space="preserve">Como é calculado</t>
   </si>
   <si>
-    <t xml:space="preserve">VOLUME (premissas do cenário)</t>
+    <t xml:space="preserve">VOLUME (premissas de cada ano, média mensal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Famílias B2C ativas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">famílias que contratam por conta própria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% das famílias B2C no Zelo+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atendimentos por família B2C por mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empresas clientes (média no ano)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ex.: piloto com 3 empresas, 5 no fim do ano 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% dos funcionários com família ativa no mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">funcionários de 35 a 60 anos que levam os pais ao médico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atendimentos por família B2B por mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o benefício estimula o uso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funcionários cobertos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Famílias B2B ativas</t>
   </si>
   <si>
     <t xml:space="preserve">Atendimentos por mês</t>
   </si>
   <si>
-    <t xml:space="preserve">~10/dia no piloto; ~270/dia no ano 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Famílias ativas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% das famílias no Zelo+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Famílias via Zelo Empresas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ex.: 2 / 10 / 50 empresas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% dos atendimentos isentos da taxa de serviço</t>
-  </si>
-  <si>
-    <t xml:space="preserve">atendimentos de famílias Zelo+ ou Empresas</t>
+    <t xml:space="preserve">Atendimentos no ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% dos atendimentos vindos do B2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% dos atendimentos isentos da taxa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">famílias Zelo+ e Zelo Empresas não pagam taxa</t>
   </si>
   <si>
     <t xml:space="preserve">ENTRADAS (dinheiro que entra)</t>
@@ -183,9 +220,6 @@
     <t xml:space="preserve">Transporte</t>
   </si>
   <si>
-    <t xml:space="preserve">atendimentos × % com transporte × preço</t>
-  </si>
-  <si>
     <t xml:space="preserve">Adicional veículo adaptado</t>
   </si>
   <si>
@@ -195,15 +229,21 @@
     <t xml:space="preserve">Assinaturas Zelo+</t>
   </si>
   <si>
-    <t xml:space="preserve">Zelo Empresas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">faturado por boleto à empresa</t>
+    <t xml:space="preserve">Zelo Empresas (mensalidade por funcionário)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">receita recorrente, faturada por boleto à empresa</t>
   </si>
   <si>
     <t xml:space="preserve">Total de entradas</t>
   </si>
   <si>
+    <t xml:space="preserve">Receita própria do Zelo (entradas − repasses − carros)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o que é de fato do Zelo</t>
+  </si>
+  <si>
     <t xml:space="preserve">SAÍDAS VARIÁVEIS</t>
   </si>
   <si>
@@ -231,31 +271,34 @@
     <t xml:space="preserve">Impostos sobre a receita própria</t>
   </si>
   <si>
-    <t xml:space="preserve">base = entradas − repasses − carros</t>
-  </si>
-  <si>
     <t xml:space="preserve">Margem de contribuição</t>
   </si>
   <si>
     <t xml:space="preserve">Margem de contribuição (% das entradas)</t>
   </si>
   <si>
-    <t xml:space="preserve">CUSTOS FIXOS (R$/mês)</t>
+    <t xml:space="preserve">CUSTOS FIXOS (média mensal no ano; azul = editável)</t>
   </si>
   <si>
     <t xml:space="preserve">Equipe de operação e atendimento (com encargos)</t>
   </si>
   <si>
-    <t xml:space="preserve">2 / 6 / 16 pessoas</t>
+    <t xml:space="preserve">2 / 5 / 9 pessoas; a Zélia faz o agendamento</t>
   </si>
   <si>
     <t xml:space="preserve">Pró-labore dos fundadores</t>
   </si>
   <si>
+    <t xml:space="preserve">3 fundadores</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tecnologia (desenvolvimento e nuvem)</t>
   </si>
   <si>
-    <t xml:space="preserve">Marketing e aquisição de famílias</t>
+    <t xml:space="preserve">Marketing e aquisição de famílias B2C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">menor porque o B2B traz famílias sem custo de aquisição</t>
   </si>
   <si>
     <t xml:space="preserve">Recrutamento e treinamento de parceiros</t>
@@ -264,10 +307,16 @@
     <t xml:space="preserve">Vendas B2B (RH)</t>
   </si>
   <si>
+    <t xml:space="preserve">1 / 2 / 3 vendedores</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jurídico, contábil e administrativo</t>
   </si>
   <si>
-    <t xml:space="preserve">Total de custos fixos</t>
+    <t xml:space="preserve">Total de custos fixos por mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total de custos fixos no ano</t>
   </si>
   <si>
     <t xml:space="preserve">RESULTADO</t>
@@ -282,34 +331,58 @@
     <t xml:space="preserve">notebooks, desenvolvimento do app</t>
   </si>
   <si>
-    <t xml:space="preserve">EBIT preliminar</t>
+    <t xml:space="preserve">EBIT</t>
   </si>
   <si>
     <t xml:space="preserve">Margem EBIT (% das entradas)</t>
   </si>
   <si>
+    <t xml:space="preserve">EBIT acumulado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vira positivo = o investimento do ano 1 se pagou</t>
+  </si>
+  <si>
     <t xml:space="preserve">PONTO DE EQUILÍBRIO</t>
   </si>
   <si>
-    <t xml:space="preserve">Margem das assinaturas (Zelo+ e Empresas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o que sobra das assinaturas depois de imposto, pagamento e IA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margem por atendimento</t>
+    <t xml:space="preserve">Margem da mensalidade B2B no ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quase toda a mensalidade vira margem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margem por atendimento (sem B2B)</t>
   </si>
   <si>
     <t xml:space="preserve">Atendimentos/mês para EBIT = 0</t>
   </si>
   <si>
-    <t xml:space="preserve">mantendo os custos fixos do cenário</t>
+    <t xml:space="preserve">mantendo os custos fixos e o B2B do ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atendimentos/mês para EBIT = 0 sem o B2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBIT se a mensalidade B2B fosse zero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">por que o Zelo Empresas é prioridade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBIT por ano conforme a mensalidade por funcionário do Zelo Empresas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada R$ 1 a mais por funcionário vira receita quase sem custo (só imposto). Demais premissas como na DRE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ por funcionário/mês</t>
   </si>
   <si>
     <t xml:space="preserve">Um atendimento: acompanhante + carro (família no plano Grátis)</t>
   </si>
   <si>
-    <t xml:space="preserve">Valores puxados da aba Premissas (verde).</t>
+    <t xml:space="preserve">Valores puxados da aba Premissas.</t>
   </si>
   <si>
     <t xml:space="preserve">Família paga: acompanhante</t>
@@ -343,14 +416,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0;&quot;(R$ &quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="&quot;R$ &quot;#,##0.00;&quot;(R$ &quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
-    <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="168" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0;\(#,##0.0\);\-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -381,7 +455,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
       <sz val="11"/>
       <color rgb="FF555555"/>
       <name val="Arial"/>
@@ -416,15 +489,8 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF008000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -443,25 +509,12 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCEFEE"/>
-        <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
@@ -491,7 +544,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -520,6 +573,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -528,31 +585,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -560,19 +625,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -580,7 +633,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -588,19 +641,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -634,7 +675,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFDCEFEE"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -856,12 +897,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -888,7 +929,7 @@
       <c r="B5" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="7" t="s">
         <v>4</v>
       </c>
     </row>
@@ -896,10 +937,10 @@
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="7" t="s">
         <v>6</v>
       </c>
     </row>
@@ -907,10 +948,10 @@
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -918,10 +959,10 @@
       <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -929,112 +970,108 @@
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="B11" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>8</v>
+      <c r="B12" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
+      <c r="A15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="B16" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B19" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1042,10 +1079,10 @@
       <c r="A20" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="B20" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1053,10 +1090,10 @@
       <c r="A21" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="B21" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1065,21 +1102,43 @@
         <v>29</v>
       </c>
       <c r="B22" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>30</v>
+        <v>4</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="9" t="n">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="12" t="n">
         <v>0.08</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>32</v>
+      <c r="C25" s="7" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1098,727 +1157,927 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="12" t="s">
+      <c r="A4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="B4" s="14" t="s">
         <v>39</v>
       </c>
+      <c r="C4" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
+      <c r="A5" s="15" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="C6" s="15" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D6" s="15" t="n">
-        <v>8000</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="15" t="n">
-        <v>200</v>
-      </c>
-      <c r="C7" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E7" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
+      <c r="A12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">B9*Premissas!$B$12</f>
+        <v>2500</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <f aca="false">C9*Premissas!$B$12</f>
+        <v>15000</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <f aca="false">D9*Premissas!$B$12</f>
+        <v>45000</v>
+      </c>
+      <c r="E12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="16" t="n">
-        <f aca="false">B6*Premissas!$B$12*Premissas!$B$5</f>
-        <v>43200</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <f aca="false">C6*Premissas!$B$12*Premissas!$B$5</f>
-        <v>216000</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <f aca="false">D6*Premissas!$B$12*Premissas!$B$5</f>
-        <v>1152000</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>51</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B13" s="17" t="n">
+        <f aca="false">B12*B10</f>
+        <v>75</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <f aca="false">C12*C10</f>
+        <v>600</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <f aca="false">D12*D10</f>
+        <v>2250</v>
+      </c>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="16" t="n">
-        <f aca="false">B6*Premissas!$B$13*Premissas!$B$6</f>
-        <v>22800</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <f aca="false">C6*Premissas!$B$13*Premissas!$B$6</f>
-        <v>114000</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <f aca="false">D6*Premissas!$B$13*Premissas!$B$6</f>
-        <v>608000</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B14" s="17" t="n">
+        <f aca="false">B6*B8+B13*B11</f>
+        <v>275</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <f aca="false">C6*C8+C13*C11</f>
+        <v>1400</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <f aca="false">D6*D8+D13*D11</f>
+        <v>4250</v>
+      </c>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="16" t="n">
-        <f aca="false">B6*Premissas!$B$14*Premissas!$B$7</f>
-        <v>1800</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <f aca="false">C6*Premissas!$B$14*Premissas!$B$7</f>
-        <v>9000</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <f aca="false">D6*Premissas!$B$14*Premissas!$B$7</f>
-        <v>48000</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="B15" s="17" t="n">
+        <f aca="false">B14*12</f>
+        <v>3300</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <f aca="false">C14*12</f>
+        <v>16800</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <f aca="false">D14*12</f>
+        <v>51000</v>
+      </c>
+      <c r="E15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="16" t="n">
-        <f aca="false">B6*(1-B10)*Premissas!$B$8</f>
-        <v>3375</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <f aca="false">C6*(1-C10)*Premissas!$B$8</f>
-        <v>13500</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <f aca="false">D6*(1-D10)*Premissas!$B$8</f>
-        <v>60000</v>
-      </c>
-      <c r="E16" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="B16" s="18" t="n">
+        <f aca="false">IF(B14=0,0,B13*B11/B14)</f>
+        <v>0.272727272727273</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <f aca="false">IF(C14=0,0,C13*C11/C14)</f>
+        <v>0.428571428571429</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <f aca="false">IF(D14=0,0,D13*D11/D14)</f>
+        <v>0.529411764705882</v>
+      </c>
+      <c r="E16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="16" t="n">
-        <f aca="false">B7*B8*Premissas!$B$9</f>
-        <v>897</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <f aca="false">C7*C8*Premissas!$B$9</f>
-        <v>5980</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <f aca="false">D7*D8*Premissas!$B$9</f>
-        <v>37375</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="16" t="n">
-        <f aca="false">B9*Premissas!$B$10</f>
-        <v>996</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <f aca="false">C9*Premissas!$B$10</f>
-        <v>9960</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <f aca="false">D9*Premissas!$B$10</f>
-        <v>62250</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="B17" s="18" t="n">
+        <f aca="false">IF(B14=0,0,(B6*B7*B8+B13*B11)/B14)</f>
+        <v>0.381818181818182</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <f aca="false">IF(C14=0,0,(C6*C7*C8+C13*C11)/C14)</f>
+        <v>0.542857142857143</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <f aca="false">IF(D14=0,0,(D6*D7*D8+D13*D11)/D14)</f>
+        <v>0.647058823529412</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="18" t="n">
-        <f aca="false">SUM(B13:B18)</f>
-        <v>73068</v>
-      </c>
-      <c r="C19" s="18" t="n">
-        <f aca="false">SUM(C13:C18)</f>
-        <v>368440</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <f aca="false">SUM(D13:D18)</f>
-        <v>1967625</v>
-      </c>
-      <c r="E19" s="2"/>
+      <c r="A19" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <f aca="false">B15*Premissas!$B$14*Premissas!$B$5</f>
+        <v>475200</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <f aca="false">C15*Premissas!$B$14*Premissas!$B$5</f>
+        <v>2419200</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <f aca="false">D15*Premissas!$B$14*Premissas!$B$5</f>
+        <v>7344000</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="A21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <f aca="false">B15*Premissas!$B$15*Premissas!$B$6</f>
+        <v>250800</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <f aca="false">C15*Premissas!$B$15*Premissas!$B$6</f>
+        <v>1276800</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <f aca="false">D15*Premissas!$B$15*Premissas!$B$6</f>
+        <v>3876000</v>
+      </c>
+      <c r="E21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="16" t="n">
-        <f aca="false">-B13*Premissas!$B$16</f>
-        <v>-32400</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <f aca="false">-C13*Premissas!$B$16</f>
-        <v>-162000</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <f aca="false">-D13*Premissas!$B$16</f>
-        <v>-864000</v>
-      </c>
-      <c r="E22" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <f aca="false">B15*Premissas!$B$16*Premissas!$B$7</f>
+        <v>19800</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <f aca="false">C15*Premissas!$B$16*Premissas!$B$7</f>
+        <v>100800</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <f aca="false">D15*Premissas!$B$16*Premissas!$B$7</f>
+        <v>306000</v>
+      </c>
+      <c r="E22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="16" t="n">
-        <f aca="false">-B6*Premissas!$B$13*Premissas!$B$17</f>
-        <v>-17100</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <f aca="false">-C6*Premissas!$B$13*Premissas!$B$17</f>
-        <v>-85500</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <f aca="false">-D6*Premissas!$B$13*Premissas!$B$17</f>
-        <v>-456000</v>
-      </c>
-      <c r="E23" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="B23" s="19" t="n">
+        <f aca="false">B15*(1-B17)*Premissas!$B$8</f>
+        <v>30600</v>
+      </c>
+      <c r="C23" s="19" t="n">
+        <f aca="false">C15*(1-C17)*Premissas!$B$8</f>
+        <v>115200</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <f aca="false">D15*(1-D17)*Premissas!$B$8</f>
+        <v>270000</v>
+      </c>
+      <c r="E23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="16" t="n">
-        <f aca="false">-B6*Premissas!$B$14*Premissas!$B$18</f>
-        <v>-1350</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <f aca="false">-C6*Premissas!$B$14*Premissas!$B$18</f>
-        <v>-6750</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <f aca="false">-D6*Premissas!$B$14*Premissas!$B$18</f>
-        <v>-36000</v>
-      </c>
-      <c r="E24" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <f aca="false">B6*B7*Premissas!$B$9*12</f>
+        <v>13455</v>
+      </c>
+      <c r="C24" s="19" t="n">
+        <f aca="false">C6*C7*Premissas!$B$9*12</f>
+        <v>71760</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <f aca="false">D6*D7*Premissas!$B$9*12</f>
+        <v>224250</v>
+      </c>
+      <c r="E24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="16" t="n">
-        <f aca="false">-(B19-B18)*Premissas!$B$19</f>
-        <v>-2162.16</v>
-      </c>
-      <c r="C25" s="16" t="n">
-        <f aca="false">-(C19-C18)*Premissas!$B$19</f>
-        <v>-10754.4</v>
-      </c>
-      <c r="D25" s="16" t="n">
-        <f aca="false">-(D19-D18)*Premissas!$B$19</f>
-        <v>-57161.25</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
+      </c>
+      <c r="B25" s="20" t="n">
+        <f aca="false">B12*Premissas!$B$11*12</f>
+        <v>150000</v>
+      </c>
+      <c r="C25" s="20" t="n">
+        <f aca="false">C12*Premissas!$B$11*12</f>
+        <v>900000</v>
+      </c>
+      <c r="D25" s="20" t="n">
+        <f aca="false">D12*Premissas!$B$11*12</f>
+        <v>2700000</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="16" t="n">
-        <f aca="false">-B6*Premissas!$B$20</f>
-        <v>-1200</v>
-      </c>
-      <c r="C26" s="16" t="n">
-        <f aca="false">-C6*Premissas!$B$20</f>
-        <v>-6000</v>
-      </c>
-      <c r="D26" s="16" t="n">
-        <f aca="false">-D6*Premissas!$B$20</f>
-        <v>-32000</v>
-      </c>
-      <c r="E26" s="2"/>
+      <c r="A26" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="21" t="n">
+        <f aca="false">SUM(B20:B25)</f>
+        <v>939855</v>
+      </c>
+      <c r="C26" s="21" t="n">
+        <f aca="false">SUM(C20:C25)</f>
+        <v>4883760</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <f aca="false">SUM(D20:D25)</f>
+        <v>14720250</v>
+      </c>
+      <c r="E26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="16" t="n">
-        <f aca="false">-(B6*Premissas!$B$21+B7*Premissas!$B$22)</f>
-        <v>-1200</v>
-      </c>
-      <c r="C27" s="16" t="n">
-        <f aca="false">-(C6*Premissas!$B$21+C7*Premissas!$B$22)</f>
-        <v>-6000</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <f aca="false">-(D6*Premissas!$B$21+D7*Premissas!$B$22)</f>
-        <v>-31500</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="16" t="n">
-        <f aca="false">-(B19+B22+B23+B24)*Premissas!$B$23</f>
-        <v>-1777.44</v>
-      </c>
-      <c r="C28" s="16" t="n">
-        <f aca="false">-(C19+C22+C23+C24)*Premissas!$B$23</f>
-        <v>-9135.2</v>
-      </c>
-      <c r="D28" s="16" t="n">
-        <f aca="false">-(D19+D22+D23+D24)*Premissas!$B$23</f>
-        <v>-48930</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <f aca="false">B26+B30+B31+B32</f>
+        <v>380505</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <f aca="false">C26+C30+C31+C32</f>
+        <v>2036160</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <f aca="false">D26+D30+D31+D32</f>
+        <v>6075750</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="18" t="n">
-        <f aca="false">B19+SUM(B22:B28)</f>
-        <v>15878.4</v>
-      </c>
-      <c r="C29" s="18" t="n">
-        <f aca="false">C19+SUM(C22:C28)</f>
-        <v>82300.4</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <f aca="false">D19+SUM(D22:D28)</f>
-        <v>442033.75</v>
-      </c>
-      <c r="E29" s="2"/>
+      <c r="A29" s="15" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B30" s="19" t="n">
-        <f aca="false">IF(B19=0,0,B29/B19)</f>
-        <v>0.217309903103958</v>
+        <f aca="false">-B20*Premissas!$B$18</f>
+        <v>-356400</v>
       </c>
       <c r="C30" s="19" t="n">
-        <f aca="false">IF(C19=0,0,C29/C19)</f>
-        <v>0.223375312126805</v>
+        <f aca="false">-C20*Premissas!$B$18</f>
+        <v>-1814400</v>
       </c>
       <c r="D30" s="19" t="n">
-        <f aca="false">IF(D19=0,0,D29/D19)</f>
-        <v>0.22465345276666</v>
-      </c>
-      <c r="E30" s="2"/>
+        <f aca="false">-D20*Premissas!$B$18</f>
+        <v>-5508000</v>
+      </c>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <f aca="false">-B15*Premissas!$B$15*Premissas!$B$19</f>
+        <v>-188100</v>
+      </c>
+      <c r="C31" s="19" t="n">
+        <f aca="false">-C15*Premissas!$B$15*Premissas!$B$19</f>
+        <v>-957600</v>
+      </c>
+      <c r="D31" s="19" t="n">
+        <f aca="false">-D15*Premissas!$B$15*Premissas!$B$19</f>
+        <v>-2907000</v>
+      </c>
+      <c r="E31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
+      <c r="A32" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="19" t="n">
+        <f aca="false">-B15*Premissas!$B$16*Premissas!$B$20</f>
+        <v>-14850</v>
+      </c>
+      <c r="C32" s="19" t="n">
+        <f aca="false">-C15*Premissas!$B$16*Premissas!$B$20</f>
+        <v>-75600</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <f aca="false">-D15*Premissas!$B$16*Premissas!$B$20</f>
+        <v>-229500</v>
+      </c>
+      <c r="E32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>14000</v>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>110000</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <f aca="false">-(B26-B25)*Premissas!$B$21</f>
+        <v>-23695.65</v>
+      </c>
+      <c r="C33" s="19" t="n">
+        <f aca="false">-(C26-C25)*Premissas!$B$21</f>
+        <v>-119512.8</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <f aca="false">-(D26-D25)*Premissas!$B$21</f>
+        <v>-360607.5</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>24000</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E34" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <f aca="false">-B15*Premissas!$B$22</f>
+        <v>-13200</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <f aca="false">-C15*Premissas!$B$22</f>
+        <v>-67200</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <f aca="false">-D15*Premissas!$B$22</f>
+        <v>-204000</v>
+      </c>
+      <c r="E34" s="7"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C35" s="7" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>70000</v>
-      </c>
-      <c r="E35" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="B35" s="19" t="n">
+        <f aca="false">-(B15*Premissas!$B$23+(B6+B13)*12*Premissas!$B$24)</f>
+        <v>-15750</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <f aca="false">-(C15*Premissas!$B$23+(C6+C13)*12*Premissas!$B$24)</f>
+        <v>-79200</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <f aca="false">-(D15*Premissas!$B$23+(D6+D13)*12*Premissas!$B$24)</f>
+        <v>-238500</v>
+      </c>
+      <c r="E35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E36" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="B36" s="19" t="n">
+        <f aca="false">-B27*Premissas!$B$25</f>
+        <v>-30440.4</v>
+      </c>
+      <c r="C36" s="19" t="n">
+        <f aca="false">-C27*Premissas!$B$25</f>
+        <v>-162892.8</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <f aca="false">-D27*Premissas!$B$25</f>
+        <v>-486060</v>
+      </c>
+      <c r="E36" s="7"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B37" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E37" s="2"/>
+      <c r="A37" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="21" t="n">
+        <f aca="false">B26+SUM(B30:B36)</f>
+        <v>297418.95</v>
+      </c>
+      <c r="C37" s="21" t="n">
+        <f aca="false">C26+SUM(C30:C36)</f>
+        <v>1607354.4</v>
+      </c>
+      <c r="D37" s="21" t="n">
+        <f aca="false">D26+SUM(D30:D36)</f>
+        <v>4786582.5</v>
+      </c>
+      <c r="E37" s="7"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="B38" s="18" t="n">
+        <f aca="false">IF(B26=0,0,B37/B26)</f>
+        <v>0.316451952694831</v>
+      </c>
+      <c r="C38" s="18" t="n">
+        <f aca="false">IF(C26=0,0,C37/C26)</f>
+        <v>0.329122315592904</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <f aca="false">IF(D26=0,0,D37/D26)</f>
+        <v>0.325169918989148</v>
+      </c>
+      <c r="E38" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" s="8" t="n">
         <v>12000</v>
       </c>
-      <c r="D38" s="7" t="n">
-        <v>35000</v>
-      </c>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B39" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="B40" s="18" t="n">
-        <f aca="false">SUM(B33:B39)</f>
-        <v>43000</v>
-      </c>
-      <c r="C40" s="18" t="n">
-        <f aca="false">SUM(C33:C39)</f>
-        <v>154000</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <f aca="false">SUM(D33:D39)</f>
-        <v>405000</v>
-      </c>
-      <c r="E40" s="2"/>
+      <c r="C41" s="8" t="n">
+        <v>32000</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
+      <c r="A42" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="21" t="n">
-        <f aca="false">B29-B40</f>
-        <v>-27121.6</v>
-      </c>
-      <c r="C43" s="21" t="n">
-        <f aca="false">C29-C40</f>
-        <v>-71699.6</v>
-      </c>
-      <c r="D43" s="21" t="n">
-        <f aca="false">D29-D40</f>
-        <v>37033.75</v>
-      </c>
-      <c r="E43" s="2"/>
+      <c r="A43" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E43" s="7"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B44" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="C44" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B45" s="22" t="n">
-        <f aca="false">B43-B44</f>
-        <v>-27621.6</v>
-      </c>
-      <c r="C45" s="22" t="n">
-        <f aca="false">C43-C44</f>
-        <v>-73699.6</v>
-      </c>
-      <c r="D45" s="22" t="n">
-        <f aca="false">D43-D44</f>
-        <v>31033.75</v>
-      </c>
-      <c r="E45" s="2"/>
+      <c r="A45" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E45" s="7"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B46" s="19" t="n">
-        <f aca="false">IF(B19=0,0,B45/B19)</f>
-        <v>-0.378025948431598</v>
-      </c>
-      <c r="C46" s="19" t="n">
-        <f aca="false">IF(C19=0,0,C45/C19)</f>
-        <v>-0.200031484095104</v>
-      </c>
-      <c r="D46" s="19" t="n">
-        <f aca="false">IF(D19=0,0,D45/D19)</f>
-        <v>0.0157721872816212</v>
-      </c>
-      <c r="E46" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E47" s="7"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
+      <c r="A48" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="19" t="n">
+        <f aca="false">SUM(B41:B47)</f>
+        <v>55000</v>
+      </c>
+      <c r="C48" s="19" t="n">
+        <f aca="false">SUM(C41:C47)</f>
+        <v>120000</v>
+      </c>
+      <c r="D48" s="19" t="n">
+        <f aca="false">SUM(D41:D47)</f>
+        <v>210000</v>
+      </c>
+      <c r="E48" s="7"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B49" s="16" t="n">
-        <f aca="false">(B17+B18)*(1-Premissas!$B$23)-B17*Premissas!$B$19-B7*Premissas!$B$22</f>
-        <v>1414.65</v>
-      </c>
-      <c r="C49" s="16" t="n">
-        <f aca="false">(C17+C18)*(1-Premissas!$B$23)-C17*Premissas!$B$19-C7*Premissas!$B$22</f>
-        <v>12985.4</v>
-      </c>
-      <c r="D49" s="16" t="n">
-        <f aca="false">(D17+D18)*(1-Premissas!$B$23)-D17*Premissas!$B$19-D7*Premissas!$B$22</f>
-        <v>83033.75</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B50" s="23" t="n">
-        <f aca="false">IF(B6=0,0,(B29-B49)/B6)</f>
-        <v>48.2125</v>
-      </c>
-      <c r="C50" s="23" t="n">
-        <f aca="false">IF(C6=0,0,(C29-C49)/C6)</f>
-        <v>46.21</v>
-      </c>
-      <c r="D50" s="23" t="n">
-        <f aca="false">IF(D6=0,0,(D29-D49)/D6)</f>
-        <v>44.875</v>
-      </c>
-      <c r="E50" s="2"/>
+      <c r="A49" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="21" t="n">
+        <f aca="false">-B48*12</f>
+        <v>-660000</v>
+      </c>
+      <c r="C49" s="21" t="n">
+        <f aca="false">-C48*12</f>
+        <v>-1440000</v>
+      </c>
+      <c r="D49" s="21" t="n">
+        <f aca="false">-D48*12</f>
+        <v>-2520000</v>
+      </c>
+      <c r="E49" s="7"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="B51" s="24" t="n">
-        <f aca="false">IF(B50&lt;=0,0,(B40+B44-B49)/B50)</f>
-        <v>872.913663469018</v>
-      </c>
-      <c r="C51" s="24" t="n">
-        <f aca="false">IF(C50&lt;=0,0,(C40+C44-C49)/C50)</f>
-        <v>3094.8842241939</v>
-      </c>
-      <c r="D51" s="24" t="n">
-        <f aca="false">IF(D50&lt;=0,0,(D40+D44-D49)/D50)</f>
-        <v>7308.44011142061</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>93</v>
+      <c r="A51" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" s="19" t="n">
+        <f aca="false">B37+B49</f>
+        <v>-362581.05</v>
+      </c>
+      <c r="C52" s="19" t="n">
+        <f aca="false">C37+C49</f>
+        <v>167354.4</v>
+      </c>
+      <c r="D52" s="19" t="n">
+        <f aca="false">D37+D49</f>
+        <v>2266582.5</v>
+      </c>
+      <c r="E52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" s="22" t="n">
+        <f aca="false">B52-B53</f>
+        <v>-368581.05</v>
+      </c>
+      <c r="C54" s="22" t="n">
+        <f aca="false">C52-C53</f>
+        <v>147354.4</v>
+      </c>
+      <c r="D54" s="22" t="n">
+        <f aca="false">D52-D53</f>
+        <v>2226582.5</v>
+      </c>
+      <c r="E54" s="7"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" s="18" t="n">
+        <f aca="false">IF(B26=0,0,B54/B26)</f>
+        <v>-0.392167993999074</v>
+      </c>
+      <c r="C55" s="18" t="n">
+        <f aca="false">IF(C26=0,0,C54/C26)</f>
+        <v>0.0301723262404378</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <f aca="false">IF(D26=0,0,D54/D26)</f>
+        <v>0.151259829146923</v>
+      </c>
+      <c r="E55" s="7"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" s="21" t="n">
+        <f aca="false">B54</f>
+        <v>-368581.05</v>
+      </c>
+      <c r="C56" s="21" t="n">
+        <f aca="false">B56+C54</f>
+        <v>-221226.65</v>
+      </c>
+      <c r="D56" s="21" t="n">
+        <f aca="false">C56+D54</f>
+        <v>2005355.85</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B59" s="19" t="n">
+        <f aca="false">B25*(1-Premissas!$B$25)</f>
+        <v>138000</v>
+      </c>
+      <c r="C59" s="19" t="n">
+        <f aca="false">C25*(1-Premissas!$B$25)</f>
+        <v>828000</v>
+      </c>
+      <c r="D59" s="19" t="n">
+        <f aca="false">D25*(1-Premissas!$B$25)</f>
+        <v>2484000</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" s="23" t="n">
+        <f aca="false">IF(B15=0,0,(B37-B59)/B15)</f>
+        <v>48.3087727272727</v>
+      </c>
+      <c r="C60" s="23" t="n">
+        <f aca="false">IF(C15=0,0,(C37-C59)/C15)</f>
+        <v>46.3901428571429</v>
+      </c>
+      <c r="D60" s="23" t="n">
+        <f aca="false">IF(D15=0,0,(D37-D59)/D15)</f>
+        <v>45.1486764705882</v>
+      </c>
+      <c r="E60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B61" s="17" t="n">
+        <f aca="false">IF(B60&lt;=0,0,(-B49+B53-B59)/B60/12)</f>
+        <v>910.807654924337</v>
+      </c>
+      <c r="C61" s="17" t="n">
+        <f aca="false">IF(C60&lt;=0,0,(-C49+C53-C59)/C60/12)</f>
+        <v>1135.29865232043</v>
+      </c>
+      <c r="D61" s="17" t="n">
+        <f aca="false">IF(D60&lt;=0,0,(-D49+D53-D59)/D60/12)</f>
+        <v>140.277275624218</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B62" s="17" t="n">
+        <f aca="false">IF(B60&lt;=0,0,(-B49+B53)/B60/12)</f>
+        <v>1148.8596556432</v>
+      </c>
+      <c r="C62" s="17" t="n">
+        <f aca="false">IF(C60&lt;=0,0,(-C49+C53)/C60/12)</f>
+        <v>2622.68359555037</v>
+      </c>
+      <c r="D62" s="17" t="n">
+        <f aca="false">IF(D60&lt;=0,0,(-D49+D53)/D60/12)</f>
+        <v>4725.12928418417</v>
+      </c>
+      <c r="E62" s="7"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B63" s="19" t="n">
+        <f aca="false">B54-B59</f>
+        <v>-506581.05</v>
+      </c>
+      <c r="C63" s="19" t="n">
+        <f aca="false">C54-C59</f>
+        <v>-680645.6</v>
+      </c>
+      <c r="D63" s="19" t="n">
+        <f aca="false">D54-D59</f>
+        <v>-257417.5</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1837,6 +2096,172 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!B54+'DRE 3 anos'!B12*12*($A5-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>-506581.05</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!C54+'DRE 3 anos'!C12*12*($A5-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>-680645.6</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!D54+'DRE 3 anos'!D12*12*($A5-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>-257417.5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!B54+'DRE 3 anos'!B12*12*($A6-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>-451381.05</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!C54+'DRE 3 anos'!C12*12*($A6-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>-349445.6</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!D54+'DRE 3 anos'!D12*12*($A6-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>736182.5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!B54+'DRE 3 anos'!B12*12*($A7-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>-423781.05</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!C54+'DRE 3 anos'!C12*12*($A7-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>-183845.6</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!D54+'DRE 3 anos'!D12*12*($A7-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>1232982.5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!B54+'DRE 3 anos'!B12*12*($A8-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>-396181.05</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!C54+'DRE 3 anos'!C12*12*($A8-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>-18245.5999999996</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!D54+'DRE 3 anos'!D12*12*($A8-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>1729782.5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!B54+'DRE 3 anos'!B12*12*($A9-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>-368581.05</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!C54+'DRE 3 anos'!C12*12*($A9-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>147354.4</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!D54+'DRE 3 anos'!D12*12*($A9-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>2226582.5</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!B54+'DRE 3 anos'!B12*12*($A10-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>-340981.05</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!C54+'DRE 3 anos'!C12*12*($A10-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>312954.4</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!D54+'DRE 3 anos'!D12*12*($A10-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>2723382.5</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!B54+'DRE 3 anos'!B12*12*($A11-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>-285781.05</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!C54+'DRE 3 anos'!C12*12*($A11-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>644154.4</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <f aca="false">'DRE 3 anos'!D54+'DRE 3 anos'!D12*12*($A11-Premissas!$B$11)*(1-Premissas!$B$25)</f>
+        <v>3716982.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1846,118 +2271,118 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" s="25" t="n">
+        <v>120</v>
+      </c>
+      <c r="B4" s="23" t="n">
         <f aca="false">Premissas!$B$5</f>
         <v>180</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="25" t="n">
+        <v>121</v>
+      </c>
+      <c r="B5" s="23" t="n">
         <f aca="false">Premissas!$B$6</f>
         <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="25" t="n">
+        <v>122</v>
+      </c>
+      <c r="B6" s="23" t="n">
         <f aca="false">Premissas!$B$8</f>
         <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="26" t="n">
+      <c r="A7" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="24" t="n">
         <f aca="false">SUM(B4:B6)</f>
         <v>275</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="B9" s="23" t="n">
-        <f aca="false">-B4*Premissas!$B$16</f>
+        <f aca="false">-B4*Premissas!$B$18</f>
         <v>-135</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="B10" s="23" t="n">
-        <f aca="false">-Premissas!$B$17</f>
+        <f aca="false">-Premissas!$B$19</f>
         <v>-60</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B11" s="23" t="n">
-        <f aca="false">-B7*Premissas!$B$19</f>
+        <f aca="false">-B7*Premissas!$B$21</f>
         <v>-8.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="B12" s="23" t="n">
-        <f aca="false">-Premissas!$B$20</f>
+        <f aca="false">-Premissas!$B$22</f>
         <v>-4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B13" s="23" t="n">
-        <f aca="false">-Premissas!$B$21</f>
+        <f aca="false">-Premissas!$B$23</f>
         <v>-3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B14" s="23" t="n">
-        <f aca="false">-(B7+B9+B10)*Premissas!$B$23</f>
+        <f aca="false">-(B7+B9+B10)*Premissas!$B$25</f>
         <v>-6.4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="27" t="n">
+      <c r="A15" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="24" t="n">
         <f aca="false">B7+SUM(B9:B14)</f>
         <v>58.35</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="19" t="n">
+        <v>128</v>
+      </c>
+      <c r="B16" s="18" t="n">
         <f aca="false">IF(B7=0,0,B15/B7)</f>
         <v>0.212181818181818</v>
       </c>
